--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2943" uniqueCount="468">
   <si>
     <t>Property</t>
   </si>
@@ -610,13 +610,7 @@
     <t>これは、検索、並べ替え、および表示の目的で使用される。</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -855,9 +849,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
-  </si>
-  <si>
     <t>DiagnosticReport.category:first.id</t>
   </si>
   <si>
@@ -1162,7 +1153,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートの作成日時</t>
+    <t>診断レポートの対象となる検査・処置が実施された日時</t>
   </si>
   <si>
     <t>観測値が関連する時間または期間。レポートの対象が患者である場合、これは通常、読影開始の時間であり、日付/時刻自体のみが提供される。</t>
@@ -1479,6 +1470,9 @@
     <t>すべての用語の使用がこの一般的なパターンに適合するわけではない。 場合によっては、モデルにcodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係と事前調整および事後調整を管理するための独自の構造を提供する必要がある。   
 【JP Core仕様】・放射線レポートの所見の結論となるコードを設定。  
 ・例えば、ICD 病名コード</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
@@ -3432,26 +3426,24 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>181</v>
@@ -3472,21 +3464,21 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>194</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3509,13 +3501,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3566,7 +3558,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3587,7 +3579,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3595,10 +3587,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3627,7 +3619,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3668,19 +3660,19 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3701,7 +3693,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -3709,10 +3701,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3735,19 +3727,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3796,7 +3788,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3814,10 +3806,10 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -3825,10 +3817,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3851,13 +3843,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3908,7 +3900,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3929,7 +3921,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -3937,10 +3929,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3969,7 +3961,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -4010,19 +4002,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4043,7 +4035,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4051,10 +4043,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4080,16 +4072,16 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4138,7 +4130,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4156,10 +4148,10 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4167,10 +4159,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4193,16 +4185,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4252,7 +4244,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4270,10 +4262,10 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4281,10 +4273,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4310,14 +4302,14 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4366,7 +4358,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4384,10 +4376,10 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4395,10 +4387,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4421,17 +4413,17 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4480,7 +4472,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4498,10 +4490,10 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4509,10 +4501,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4535,19 +4527,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4596,7 +4588,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4614,10 +4606,10 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4625,10 +4617,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4651,19 +4643,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4712,7 +4704,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4730,10 +4722,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4741,13 +4733,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>181</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>182</v>
@@ -4772,10 +4764,10 @@
         <v>183</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>186</v>
@@ -4789,7 +4781,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4808,7 +4800,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>265</v>
+        <v>187</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4844,21 +4836,21 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>194</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4881,13 +4873,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4938,7 +4930,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4959,7 +4951,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -4967,10 +4959,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4999,7 +4991,7 @@
         <v>138</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>140</v>
@@ -5040,19 +5032,19 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5073,7 +5065,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5081,10 +5073,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5107,19 +5099,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5168,7 +5160,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5186,10 +5178,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5197,10 +5189,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5223,13 +5215,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5280,7 +5272,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5301,7 +5293,7 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5309,10 +5301,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5341,7 +5333,7 @@
         <v>138</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>140</v>
@@ -5382,19 +5374,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5415,7 +5407,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5423,10 +5415,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5452,16 +5444,16 @@
         <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5510,7 +5502,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5528,10 +5520,10 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5539,10 +5531,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5565,16 +5557,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5624,7 +5616,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5642,10 +5634,10 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5653,10 +5645,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5682,14 +5674,14 @@
         <v>111</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5738,7 +5730,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5756,10 +5748,10 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5767,10 +5759,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5793,17 +5785,17 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5852,7 +5844,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5870,10 +5862,10 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -5881,10 +5873,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5907,19 +5899,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5968,7 +5960,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5986,10 +5978,10 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -5997,10 +5989,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6023,19 +6015,19 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6084,7 +6076,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6102,10 +6094,10 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6113,13 +6105,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>181</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>182</v>
@@ -6144,10 +6136,10 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>186</v>
@@ -6180,7 +6172,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6216,21 +6208,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>194</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6253,13 +6245,13 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6310,7 +6302,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6331,7 +6323,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6339,10 +6331,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6371,7 +6363,7 @@
         <v>138</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>140</v>
@@ -6412,19 +6404,19 @@
         <v>81</v>
       </c>
       <c r="AB40" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6445,7 +6437,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6453,10 +6445,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6479,19 +6471,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6540,7 +6532,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6558,10 +6550,10 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6569,10 +6561,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6595,13 +6587,13 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6652,7 +6644,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6673,7 +6665,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -6681,10 +6673,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6713,7 +6705,7 @@
         <v>138</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>140</v>
@@ -6754,19 +6746,19 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6787,7 +6779,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -6795,10 +6787,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6824,23 +6816,23 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>81</v>
@@ -6882,7 +6874,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6900,10 +6892,10 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -6911,10 +6903,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6937,16 +6929,16 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6996,7 +6988,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7014,10 +7006,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7025,10 +7017,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7054,14 +7046,14 @@
         <v>111</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7110,7 +7102,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7128,10 +7120,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7139,10 +7131,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7165,17 +7157,17 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7224,7 +7216,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7242,10 +7234,10 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7253,10 +7245,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7279,19 +7271,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7340,7 +7332,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7358,10 +7350,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7369,10 +7361,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7395,19 +7387,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -7456,7 +7448,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7474,10 +7466,10 @@
         <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7485,14 +7477,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7514,13 +7506,13 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7550,7 +7542,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7568,7 +7560,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>91</v>
@@ -7583,24 +7575,24 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7623,13 +7615,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7680,7 +7672,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7701,7 +7693,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -7709,10 +7701,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7741,7 +7733,7 @@
         <v>138</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>140</v>
@@ -7782,19 +7774,19 @@
         <v>81</v>
       </c>
       <c r="AB52" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7815,7 +7807,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7823,10 +7815,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7849,19 +7841,19 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -7898,17 +7890,17 @@
         <v>81</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7926,10 +7918,10 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7937,13 +7929,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B54" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>81</v>
@@ -7965,19 +7957,19 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8026,7 +8018,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8044,10 +8036,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -8055,10 +8047,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8081,13 +8073,13 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8138,7 +8130,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8159,7 +8151,7 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8167,10 +8159,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8199,7 +8191,7 @@
         <v>138</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>140</v>
@@ -8240,19 +8232,19 @@
         <v>81</v>
       </c>
       <c r="AB56" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8273,7 +8265,7 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -8281,10 +8273,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8310,23 +8302,23 @@
         <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>81</v>
@@ -8368,7 +8360,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8386,10 +8378,10 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -8397,10 +8389,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8423,16 +8415,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8482,7 +8474,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8500,10 +8492,10 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -8511,10 +8503,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8540,21 +8532,21 @@
         <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>81</v>
@@ -8596,7 +8588,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8614,10 +8606,10 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -8625,10 +8617,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8651,17 +8643,17 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -8671,7 +8663,7 @@
         <v>81</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>81</v>
@@ -8710,7 +8702,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8728,10 +8720,10 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -8739,10 +8731,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8765,19 +8757,19 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8826,7 +8818,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8844,10 +8836,10 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -8855,10 +8847,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8881,19 +8873,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -8942,7 +8934,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8960,10 +8952,10 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -8971,14 +8963,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8997,19 +8989,19 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9058,7 +9050,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9073,28 +9065,28 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>349</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9113,19 +9105,19 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9174,7 +9166,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9189,28 +9181,28 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9229,19 +9221,19 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9290,7 +9282,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9305,28 +9297,28 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9345,19 +9337,19 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -9406,7 +9398,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9424,25 +9416,25 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9461,19 +9453,19 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -9522,7 +9514,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9537,28 +9529,28 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>392</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9577,19 +9569,19 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -9638,7 +9630,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9653,24 +9645,24 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>392</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9693,19 +9685,19 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9754,7 +9746,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9772,10 +9764,10 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -9783,14 +9775,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9809,19 +9801,19 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -9870,7 +9862,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -9888,10 +9880,10 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -9899,10 +9891,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9925,16 +9917,16 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9984,7 +9976,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10005,7 +9997,7 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10013,14 +10005,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10039,19 +10031,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10100,7 +10092,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10118,10 +10110,10 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
@@ -10129,10 +10121,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10155,13 +10147,13 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10212,7 +10204,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10233,7 +10225,7 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -10241,10 +10233,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10273,7 +10265,7 @@
         <v>138</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -10326,7 +10318,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10347,7 +10339,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -10355,14 +10347,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10384,10 +10376,10 @@
         <v>137</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>140</v>
@@ -10442,7 +10434,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10471,10 +10463,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10497,19 +10489,19 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O76" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -10558,7 +10550,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10579,7 +10571,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -10587,10 +10579,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10613,16 +10605,16 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10672,7 +10664,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>91</v>
@@ -10693,7 +10685,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -10701,14 +10693,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10727,19 +10719,19 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -10788,7 +10780,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10806,10 +10798,10 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -10817,10 +10809,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10846,13 +10838,13 @@
         <v>183</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10878,13 +10870,13 @@
         <v>81</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>187</v>
+        <v>457</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>81</v>
@@ -10902,7 +10894,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10920,10 +10912,10 @@
         <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -10931,10 +10923,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10957,19 +10949,19 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11018,7 +11010,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11036,10 +11028,10 @@
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
